--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130490114</v>
       </c>
       <c r="B3" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>57035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R2" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B3" t="n">
-        <v>57033</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,43 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R3" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>57035</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R2" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>57035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,34 +787,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R3" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R2" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B3" t="n">
-        <v>57035</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,43 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R3" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R2" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B3" t="n">
-        <v>57035</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,43 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R3" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>57043</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R2" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,34 +787,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R3" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R2" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,43 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R3" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130490114</v>
+        <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686251</v>
+        <v>686263</v>
       </c>
       <c r="R2" t="n">
-        <v>7143887</v>
+        <v>7143884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130490112</v>
+        <v>130490114</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,34 +787,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686263</v>
+        <v>686251</v>
       </c>
       <c r="R3" t="n">
-        <v>7143884</v>
+        <v>7143887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12760-2022 artfynd.xlsx
+++ b/artfynd/A 12760-2022 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>130490112</v>
       </c>
       <c r="B2" t="n">
-        <v>79237</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -779,11 +779,11 @@
         <v>130490114</v>
       </c>
       <c r="B3" t="n">
-        <v>57058</v>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
